--- a/miniproject1/새 Microsoft Excel 워크시트.xlsx
+++ b/miniproject1/새 Microsoft Excel 워크시트.xlsx
@@ -4,10 +4,13 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="317">
   <si>
     <t>미니 프로젝트 기획안</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -237,10 +240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>티명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>등록일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -542,6 +541,754 @@
   </si>
   <si>
     <t>(DTO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 기본정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인화면 - 학생데이터 입력/조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자, 교사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 기본 정보를 입력하고 목록을 조회, 수정, 삭제하는 화면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 경로 및 주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진입경로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이드메뉴 학생 관리 클릭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/students</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STUDENT-INPUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 주요 화면 요소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구성요소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록검색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로고침버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이징</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름, 반, 팀 작성 하고 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름으로 학생 검색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록 된 학생 목록 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목록 새로고침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에 5명씩 제공하고 나머지는 페이징 번호처리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 주요기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 정보 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 목록 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름 검색</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">필수 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답 데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class_n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>team</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>class_n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>team</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. API</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소및메서드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생목록 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GET / students</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POST / students</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"name" : "이동렬", "class_n" : "AIOT 2회차", "team" : "B"}</t>
+  </si>
+  <si>
+    <t>{"name" : "이동렬", "class_n" : "AIOT 2회차", "team" : "B"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ { "id":"1, "name":"차도헌", "class_n":AIOT 2회차", "team":"A팀", "create_at":"2026-05-18"  }, ... ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. 예외처리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름을 입력하지 않은 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"이름을 입력해주세요" 메시지 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>반을 입력하지 않은 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"반을 입력 해주세요" 메시지 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀을 입력하지 않은 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"팀을 입력 해주세요" 메시지 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 이름 중복 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서버오류 발생 시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"서버 오류가 발생했습니다. 다시 시도해주세요" 페이지 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"이미 등록된 학생입니다." 메시지 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인화면 - 성적 데이터 입력 화면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCORE_INPUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생별 과목 점수를 입력하고, 등록된 성적 데이터를 조회하여 성적 및 평균 점수 출력하는 화면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진입 경로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이드 메뉴에서 성적 입력 클릭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/scores</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 화면 구성 요소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록된 학생 목록 중 성적을 입력할 학생 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>python 점수입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>python 과목 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numpy 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>numpy 과목 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pandas 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pandas 과목 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java 과목 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>project 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>project 과목 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 저장 버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력한 성적 데이터를 FastAPI로 전송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 목록 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록된 학생별 성적 데이터(과목점수, 평균점수) 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 주요 기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>과목별 점수 입력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 목록 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생별 평균 점수 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수 입력값 검증</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입력데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필드명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>student_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생ID(PK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pandas_score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파이썬 점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>넘파이 점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판다스 점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자바 점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트 점수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>student_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 ID (PK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생ID (PK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>total_score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avg_score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메서드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>요청주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응답예시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/scores</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"student_id":1, "python_score":90, "numpy_score":85, "pandas_score":80, "java_score":94, "project_socre":96 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ {"student_id":1, "student_id":1, "student_namd":"이창호 ,"python_score":90, "numpy_score":85, "pandas_score":80, "java_score":94, "project_socre":96, "total_score":450, "avg_score":85.3 }, ... ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 점수 범위 오류
+{ "message":"python_score 점수는 0점 이상 100점 이하만 가능합니다. }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 데이터 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성적 목록 조회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. 예외 처리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처리내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수가 0 미만인 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0점 이상 입력 가능합니다 반환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>점수만 100 초과인 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100점 이하만 입력 가능 합니다. 반환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자가 아닌 값 입력 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자만 입력 가능합니다. 반환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수 과목 점수 누락</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 과목 점수를 입력해주세요 반환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>존재하지 않는 학생 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생 정보를 찾을 수 없습니다. 반환</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -565,7 +1312,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,8 +1325,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -587,19 +1340,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -615,6 +1498,237 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="생성된 이미지: 학생 학습 분석 대시보드"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="AutoShape 5" descr="생성된 이미지: 학생 학습 분석 대시보드"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>141314</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6162674" cy="4122764"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>101601</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="6124575" cy="4083050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6172200" cy="4114800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -973,11 +2087,11 @@
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="11"/>
+      <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1113,7 +2227,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>49</v>
@@ -1122,313 +2236,313 @@
         <v>53</v>
       </c>
       <c r="E27" t="s">
+        <v>222</v>
+      </c>
+      <c r="F27" t="s">
         <v>54</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" t="s">
         <v>56</v>
       </c>
-      <c r="C28" t="s">
-        <v>57</v>
-      </c>
       <c r="D28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" t="s">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s">
         <v>65</v>
-      </c>
-      <c r="H28" t="s">
-        <v>83</v>
-      </c>
-      <c r="I28" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" t="s">
         <v>67</v>
-      </c>
-      <c r="H29" t="s">
-        <v>84</v>
-      </c>
-      <c r="I29" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" t="s">
         <v>71</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>72</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>73</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>74</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>75</v>
       </c>
-      <c r="G30" t="s">
-        <v>76</v>
-      </c>
       <c r="H30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>49</v>
       </c>
       <c r="D31" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" t="s">
         <v>78</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>79</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>80</v>
       </c>
-      <c r="G31" t="s">
-        <v>81</v>
-      </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" t="s">
         <v>86</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>87</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
         <v>88</v>
-      </c>
-      <c r="E33" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" t="s">
         <v>94</v>
-      </c>
-      <c r="E34" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" t="s">
         <v>101</v>
-      </c>
-      <c r="E38" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="E40" t="s">
         <v>105</v>
-      </c>
-      <c r="E40" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C45" s="4" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C45" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C47" s="4" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C47" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C51" s="4" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C51" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C56" s="4" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C56" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C60" s="4" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C60" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D61" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1439,4 +2553,2203 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="J1:T46"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="15" width="11.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J1" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+    </row>
+    <row r="2" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J2" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="24"/>
+    </row>
+    <row r="3" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J3" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="24"/>
+    </row>
+    <row r="4" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="24"/>
+    </row>
+    <row r="5" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="24"/>
+    </row>
+    <row r="6" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="24"/>
+    </row>
+    <row r="8" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J9" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="14"/>
+    </row>
+    <row r="10" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J10" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="14"/>
+    </row>
+    <row r="12" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J13" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+    </row>
+    <row r="14" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+    </row>
+    <row r="15" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J15" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+    </row>
+    <row r="16" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+    </row>
+    <row r="17" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J17" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+    </row>
+    <row r="18" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J18" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+    </row>
+    <row r="20" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J26" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="P26" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+    </row>
+    <row r="27" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J27" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="N27" s="15"/>
+      <c r="P27" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="S27" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="T27" s="15"/>
+    </row>
+    <row r="28" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J28" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="N28" s="15"/>
+      <c r="P28" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="S28" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="T28" s="15"/>
+    </row>
+    <row r="29" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J29" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="N29" s="15"/>
+      <c r="P29" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="S29" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="T29" s="15"/>
+    </row>
+    <row r="30" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J30" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="N30" s="15"/>
+      <c r="P30" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="S30" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="T30" s="15"/>
+    </row>
+    <row r="31" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P31" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q31" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="S31" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="T31" s="15"/>
+    </row>
+    <row r="32" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P32" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q32" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="S32" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="T32" s="15"/>
+    </row>
+    <row r="35" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J36" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+    </row>
+    <row r="37" spans="10:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J37" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="L37" s="18"/>
+      <c r="M37" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="N37" s="17"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="18"/>
+    </row>
+    <row r="38" spans="10:20" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J38" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="L38" s="18"/>
+      <c r="M38" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="N38" s="17"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="18"/>
+    </row>
+    <row r="40" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J41" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15"/>
+    </row>
+    <row r="42" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J42" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
+    </row>
+    <row r="43" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J43" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="15"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
+      <c r="T43" s="15"/>
+    </row>
+    <row r="44" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J44" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+    </row>
+    <row r="45" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J45" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="15"/>
+      <c r="R45" s="15"/>
+      <c r="S45" s="15"/>
+      <c r="T45" s="15"/>
+    </row>
+    <row r="46" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J46" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="14"/>
+      <c r="N46" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+      <c r="S46" s="15"/>
+      <c r="T46" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="46">
+    <mergeCell ref="K2:T2"/>
+    <mergeCell ref="K3:T3"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="K16:T16"/>
+    <mergeCell ref="K17:T17"/>
+    <mergeCell ref="K18:T18"/>
+    <mergeCell ref="J26:N26"/>
+    <mergeCell ref="K9:T9"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="K14:T14"/>
+    <mergeCell ref="K15:T15"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="P26:T26"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="P36:T36"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="P37:T37"/>
+    <mergeCell ref="P38:T38"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="N41:T41"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="N42:T42"/>
+    <mergeCell ref="N43:T43"/>
+    <mergeCell ref="N44:T44"/>
+    <mergeCell ref="N45:T45"/>
+    <mergeCell ref="N46:T46"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="J45:M45"/>
+    <mergeCell ref="J46:M46"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="J1:T57"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="10" max="10" width="13.875" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J2" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="14"/>
+    </row>
+    <row r="3" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J3" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="24"/>
+    </row>
+    <row r="4" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J4" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="24"/>
+    </row>
+    <row r="5" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="24"/>
+    </row>
+    <row r="6" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J6" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="24"/>
+    </row>
+    <row r="7" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J7" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="24"/>
+    </row>
+    <row r="9" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="24"/>
+    </row>
+    <row r="11" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J11" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="24"/>
+    </row>
+    <row r="13" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J14" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="14"/>
+    </row>
+    <row r="15" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J15" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="K15" s="14"/>
+      <c r="L15" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="14"/>
+    </row>
+    <row r="16" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J16" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="K16" s="14"/>
+      <c r="L16" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="14"/>
+    </row>
+    <row r="17" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J17" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="K17" s="14"/>
+      <c r="L17" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="14"/>
+    </row>
+    <row r="18" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J18" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="14"/>
+    </row>
+    <row r="19" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J19" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="14"/>
+    </row>
+    <row r="20" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J20" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="14"/>
+    </row>
+    <row r="21" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J21" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="K21" s="14"/>
+      <c r="L21" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="14"/>
+    </row>
+    <row r="22" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J22" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="K22" s="14"/>
+      <c r="L22" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="14"/>
+    </row>
+    <row r="24" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="28" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="32" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J33" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="14"/>
+      <c r="P33" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="14"/>
+    </row>
+    <row r="34" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J34" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="N34" s="14"/>
+      <c r="P34" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="S34" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="T34" s="14"/>
+    </row>
+    <row r="35" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J35" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="M35" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="N35" s="14"/>
+      <c r="P35" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="S35" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="T35" s="14"/>
+    </row>
+    <row r="36" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J36" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="M36" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="N36" s="14"/>
+      <c r="P36" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="S36" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="T36" s="14"/>
+    </row>
+    <row r="37" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J37" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="N37" s="14"/>
+      <c r="P37" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="S37" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="T37" s="14"/>
+    </row>
+    <row r="38" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J38" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="N38" s="14"/>
+      <c r="P38" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="S38" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="T38" s="14"/>
+    </row>
+    <row r="39" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="N39" s="14"/>
+      <c r="P39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R39" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="S39" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="T39" s="14"/>
+    </row>
+    <row r="40" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J40" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="N40" s="14"/>
+      <c r="P40" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="S40" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="T40" s="14"/>
+    </row>
+    <row r="41" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P41" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="S41" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="T41" s="14"/>
+    </row>
+    <row r="42" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P42" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="S42" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="T42" s="14"/>
+    </row>
+    <row r="43" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P43" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="R43" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="S43" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="T43" s="14"/>
+    </row>
+    <row r="44" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P44" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="S44" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="T44" s="14"/>
+    </row>
+    <row r="46" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J47" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="R47" s="13"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="14"/>
+    </row>
+    <row r="48" spans="10:20" s="30" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J48" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="L48" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="29"/>
+    </row>
+    <row r="49" spans="10:20" s="30" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J49" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="L49" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="M49" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="18"/>
+    </row>
+    <row r="51" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J52" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="14"/>
+    </row>
+    <row r="53" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J53" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="14"/>
+    </row>
+    <row r="54" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J54" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="14"/>
+    </row>
+    <row r="55" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J55" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="14"/>
+    </row>
+    <row r="56" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J56" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="14"/>
+    </row>
+    <row r="57" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J57" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+      <c r="R57" s="13"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="64">
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="N55:T55"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="N56:T56"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="N57:T57"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="N52:T52"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="N53:T53"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="N54:T54"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="Q47:T47"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="Q48:T48"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q49:T49"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="S43:T43"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="P33:T33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:T22"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:T19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:T20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:T21"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:T16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:T17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:T18"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:T14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:T15"/>
+    <mergeCell ref="K2:T2"/>
+    <mergeCell ref="K3:T3"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="K7:T7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="J1:T57"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J2" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="14"/>
+    </row>
+    <row r="3" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J3" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="K3" s="22"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="24"/>
+    </row>
+    <row r="4" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J4" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="K4" s="22"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="24"/>
+    </row>
+    <row r="5" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="24"/>
+    </row>
+    <row r="6" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J6" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="24"/>
+    </row>
+    <row r="7" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J7" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="24"/>
+    </row>
+    <row r="9" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J10" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="K10" s="22"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="24"/>
+    </row>
+    <row r="11" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J11" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="K11" s="25"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="24"/>
+    </row>
+    <row r="13" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J14" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="14"/>
+      <c r="L14" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="14"/>
+    </row>
+    <row r="15" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J15" s="12"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="14"/>
+    </row>
+    <row r="16" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J16" s="12"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="14"/>
+    </row>
+    <row r="17" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J17" s="12"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="14"/>
+    </row>
+    <row r="18" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J18" s="12"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="14"/>
+    </row>
+    <row r="19" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J19" s="12"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="14"/>
+    </row>
+    <row r="20" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J20" s="12"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="14"/>
+    </row>
+    <row r="21" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J21" s="12"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="14"/>
+    </row>
+    <row r="22" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J22" s="12"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="14"/>
+    </row>
+    <row r="24" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J33" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="14"/>
+      <c r="P33" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="14"/>
+    </row>
+    <row r="34" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J34" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="M34" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="N34" s="14"/>
+      <c r="P34" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="R34" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="S34" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="T34" s="14"/>
+    </row>
+    <row r="35" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J35" s="5"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="14"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="14"/>
+    </row>
+    <row r="36" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J36" s="5"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="14"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="14"/>
+    </row>
+    <row r="37" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J37" s="5"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="14"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="12"/>
+      <c r="T37" s="14"/>
+    </row>
+    <row r="38" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J38" s="5"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="14"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="12"/>
+      <c r="T38" s="14"/>
+    </row>
+    <row r="39" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J39" s="5"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="12"/>
+      <c r="N39" s="14"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="12"/>
+      <c r="T39" s="14"/>
+    </row>
+    <row r="40" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J40" s="5"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="14"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="14"/>
+    </row>
+    <row r="41" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P41" s="5"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="12"/>
+      <c r="T41" s="14"/>
+    </row>
+    <row r="42" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P42" s="5"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="12"/>
+      <c r="T42" s="14"/>
+    </row>
+    <row r="43" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P43" s="5"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="12"/>
+      <c r="T43" s="14"/>
+    </row>
+    <row r="44" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="P44" s="5"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="12"/>
+      <c r="T44" s="14"/>
+    </row>
+    <row r="46" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J47" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="R47" s="13"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="14"/>
+    </row>
+    <row r="48" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="29"/>
+    </row>
+    <row r="49" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="18"/>
+    </row>
+    <row r="51" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J52" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="14"/>
+    </row>
+    <row r="53" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J53" s="12"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
+      <c r="R53" s="13"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="14"/>
+    </row>
+    <row r="54" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J54" s="12"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
+      <c r="R54" s="13"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="14"/>
+    </row>
+    <row r="55" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J55" s="12"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
+      <c r="R55" s="13"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="14"/>
+    </row>
+    <row r="56" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J56" s="12"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
+      <c r="R56" s="13"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="14"/>
+    </row>
+    <row r="57" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J57" s="12"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+      <c r="R57" s="13"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="64">
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="N56:T56"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="N57:T57"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="N53:T53"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="N54:T54"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="N55:T55"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="Q48:T48"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="Q49:T49"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="N52:T52"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="S43:T43"/>
+    <mergeCell ref="S44:T44"/>
+    <mergeCell ref="M47:P47"/>
+    <mergeCell ref="Q47:T47"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:T22"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="P33:T33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:T19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:T20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:T21"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:T16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:T17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:T18"/>
+    <mergeCell ref="K10:T10"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:T14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:T15"/>
+    <mergeCell ref="K2:T2"/>
+    <mergeCell ref="K3:T3"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
+    <mergeCell ref="K6:T6"/>
+    <mergeCell ref="K7:T7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>